--- a/backend/data/vmliste_remplie.xlsx
+++ b/backend/data/vmliste_remplie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PFE\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D2320E-E730-4BE4-A6C9-EF6089CDA0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D80A9DD-BDEC-47ED-9ECD-27AFC3C5AFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1978D2A-6F69-41FB-B8AC-CD413F16B440}"/>
   </bookViews>
@@ -7943,13 +7943,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EDF85139-DD09-4B7E-82A3-D7FC22DE1250}" name="vmliste_filtre_corrige" displayName="vmliste_filtre_corrige" ref="A1:CM201" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:CM201" xr:uid="{EDF85139-DD09-4B7E-82A3-D7FC22DE1250}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="LOG"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:CM201" xr:uid="{EDF85139-DD09-4B7E-82A3-D7FC22DE1250}"/>
   <tableColumns count="91">
     <tableColumn id="1" xr3:uid="{5F1974A1-3B9C-401C-9FFF-738EA6D0549C}" uniqueName="1" name="NAME" queryTableFieldId="1" dataDxfId="79"/>
     <tableColumn id="2" xr3:uid="{DA2A3AAA-C021-458A-99FB-F075456F997E}" uniqueName="2" name="IP" queryTableFieldId="2" dataDxfId="78"/>
@@ -8732,7 +8726,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -9004,7 +8998,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>137</v>
       </c>
@@ -9276,7 +9270,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>173</v>
       </c>
@@ -9548,7 +9542,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="5" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>208</v>
       </c>
@@ -9820,7 +9814,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="6" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>246</v>
       </c>
@@ -10092,7 +10086,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="7" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>283</v>
       </c>
@@ -10367,7 +10361,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="8" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>315</v>
       </c>
@@ -10639,7 +10633,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="9" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>345</v>
       </c>
@@ -10911,7 +10905,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="10" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>372</v>
       </c>
@@ -11186,7 +11180,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="11" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>400</v>
       </c>
@@ -11730,7 +11724,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="13" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>457</v>
       </c>
@@ -12005,7 +11999,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="14" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>486</v>
       </c>
@@ -12277,7 +12271,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="15" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>513</v>
       </c>
@@ -12549,7 +12543,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="16" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>539</v>
       </c>
@@ -12821,7 +12815,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="17" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>560</v>
       </c>
@@ -13093,7 +13087,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="18" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>582</v>
       </c>
@@ -13365,7 +13359,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="19" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>603</v>
       </c>
@@ -13640,7 +13634,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="20" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>624</v>
       </c>
@@ -13912,7 +13906,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="21" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>645</v>
       </c>
@@ -14184,7 +14178,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="22" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>665</v>
       </c>
@@ -14459,7 +14453,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="23" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>687</v>
       </c>
@@ -15003,7 +14997,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="25" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>727</v>
       </c>
@@ -15278,7 +15272,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="26" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>751</v>
       </c>
@@ -15550,7 +15544,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="27" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>772</v>
       </c>
@@ -15822,7 +15816,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="28" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>793</v>
       </c>
@@ -16094,7 +16088,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="29" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>814</v>
       </c>
@@ -16366,7 +16360,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="30" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>835</v>
       </c>
@@ -16638,7 +16632,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="31" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>856</v>
       </c>
@@ -16913,7 +16907,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="32" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>877</v>
       </c>
@@ -17185,7 +17179,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="33" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>898</v>
       </c>
@@ -17457,7 +17451,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="34" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>918</v>
       </c>
@@ -17732,7 +17726,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="35" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>940</v>
       </c>
@@ -18276,7 +18270,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="37" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>982</v>
       </c>
@@ -18551,7 +18545,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="38" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1005</v>
       </c>
@@ -18823,7 +18817,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="39" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1025</v>
       </c>
@@ -19095,7 +19089,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="40" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1049</v>
       </c>
@@ -19367,7 +19361,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="41" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1069</v>
       </c>
@@ -19639,7 +19633,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="42" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1089</v>
       </c>
@@ -19911,7 +19905,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="43" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1108</v>
       </c>
@@ -20186,7 +20180,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="44" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1131</v>
       </c>
@@ -20458,7 +20452,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="45" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1152</v>
       </c>
@@ -20730,7 +20724,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="46" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1171</v>
       </c>
@@ -21005,7 +20999,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="47" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1192</v>
       </c>
@@ -21549,7 +21543,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="49" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1230</v>
       </c>
@@ -21824,7 +21818,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="50" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1250</v>
       </c>
@@ -22096,7 +22090,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="51" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1269</v>
       </c>
@@ -22368,7 +22362,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="52" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1290</v>
       </c>
@@ -22640,7 +22634,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="53" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1310</v>
       </c>
@@ -22912,7 +22906,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="54" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1329</v>
       </c>
@@ -23184,7 +23178,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="55" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1348</v>
       </c>
@@ -23459,7 +23453,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="56" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1368</v>
       </c>
@@ -23731,7 +23725,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="57" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1388</v>
       </c>
@@ -24003,7 +23997,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="58" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1408</v>
       </c>
@@ -24278,7 +24272,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="59" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1429</v>
       </c>
@@ -24822,7 +24816,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="61" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1467</v>
       </c>
@@ -25097,7 +25091,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="62" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1487</v>
       </c>
@@ -25369,7 +25363,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="63" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1506</v>
       </c>
@@ -25641,7 +25635,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="64" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1525</v>
       </c>
@@ -25913,7 +25907,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="65" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1544</v>
       </c>
@@ -26185,7 +26179,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="66" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1561</v>
       </c>
@@ -26457,7 +26451,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="67" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1579</v>
       </c>
@@ -26732,7 +26726,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="68" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1598</v>
       </c>
@@ -27004,7 +26998,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="69" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1616</v>
       </c>
@@ -27276,7 +27270,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="70" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1634</v>
       </c>
@@ -27551,7 +27545,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="71" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1652</v>
       </c>
@@ -28095,7 +28089,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="73" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>1687</v>
       </c>
@@ -28370,7 +28364,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="74" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1706</v>
       </c>
@@ -28642,7 +28636,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="75" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1729</v>
       </c>
@@ -28914,7 +28908,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="76" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>1747</v>
       </c>
@@ -29186,7 +29180,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="77" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1765</v>
       </c>
@@ -29458,7 +29452,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="78" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1779</v>
       </c>
@@ -29730,7 +29724,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="79" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1797</v>
       </c>
@@ -30005,7 +29999,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="80" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1816</v>
       </c>
@@ -30277,7 +30271,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="81" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>1835</v>
       </c>
@@ -30549,7 +30543,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="82" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1853</v>
       </c>
@@ -30821,7 +30815,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="83" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>1857</v>
       </c>
@@ -31093,7 +31087,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="84" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1860</v>
       </c>
@@ -31365,7 +31359,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="85" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1864</v>
       </c>
@@ -31640,7 +31634,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="86" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1868</v>
       </c>
@@ -31912,7 +31906,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="87" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1872</v>
       </c>
@@ -32184,7 +32178,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="88" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1876</v>
       </c>
@@ -32459,7 +32453,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="89" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1880</v>
       </c>
@@ -33003,7 +32997,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="91" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1888</v>
       </c>
@@ -33278,7 +33272,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="92" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1892</v>
       </c>
@@ -33550,7 +33544,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="93" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1896</v>
       </c>
@@ -33822,7 +33816,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="94" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1900</v>
       </c>
@@ -34094,7 +34088,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="95" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1904</v>
       </c>
@@ -34366,7 +34360,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="96" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1907</v>
       </c>
@@ -34638,7 +34632,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="97" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1911</v>
       </c>
@@ -34913,7 +34907,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="98" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1915</v>
       </c>
@@ -35185,7 +35179,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="99" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1919</v>
       </c>
@@ -35457,7 +35451,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="100" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1923</v>
       </c>
@@ -35732,7 +35726,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="101" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1927</v>
       </c>
@@ -36276,7 +36270,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="103" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1935</v>
       </c>
@@ -36551,7 +36545,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="104" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1940</v>
       </c>
@@ -36823,7 +36817,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="105" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1944</v>
       </c>
@@ -37095,7 +37089,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="106" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1948</v>
       </c>
@@ -37367,7 +37361,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="107" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1952</v>
       </c>
@@ -37639,7 +37633,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="108" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1955</v>
       </c>
@@ -37911,7 +37905,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="109" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1959</v>
       </c>
@@ -38186,7 +38180,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="110" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1963</v>
       </c>
@@ -38458,7 +38452,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="111" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1967</v>
       </c>
@@ -38730,7 +38724,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="112" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1971</v>
       </c>
@@ -39005,7 +38999,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="113" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1975</v>
       </c>
@@ -39549,7 +39543,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="115" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1983</v>
       </c>
@@ -39824,7 +39818,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="116" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1987</v>
       </c>
@@ -40096,7 +40090,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="117" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1991</v>
       </c>
@@ -40368,7 +40362,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="118" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1995</v>
       </c>
@@ -40640,7 +40634,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="119" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1999</v>
       </c>
@@ -40912,7 +40906,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="120" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>2002</v>
       </c>
@@ -41184,7 +41178,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="121" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2006</v>
       </c>
@@ -41459,7 +41453,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="122" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2010</v>
       </c>
@@ -41731,7 +41725,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="123" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>2014</v>
       </c>
@@ -42003,7 +41997,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="124" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>2018</v>
       </c>
@@ -42278,7 +42272,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="125" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>2022</v>
       </c>
@@ -42822,7 +42816,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="127" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>2030</v>
       </c>
@@ -43097,7 +43091,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="128" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2034</v>
       </c>
@@ -43369,7 +43363,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="129" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2038</v>
       </c>
@@ -43641,7 +43635,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="130" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>2042</v>
       </c>
@@ -43913,7 +43907,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="131" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2046</v>
       </c>
@@ -44185,7 +44179,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="132" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>2049</v>
       </c>
@@ -44457,7 +44451,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="133" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>2053</v>
       </c>
@@ -44732,7 +44726,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="134" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>2057</v>
       </c>
@@ -45004,7 +44998,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="135" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>2061</v>
       </c>
@@ -45276,7 +45270,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="136" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>2065</v>
       </c>
@@ -45551,7 +45545,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="137" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>2069</v>
       </c>
@@ -46095,7 +46089,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="139" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>2077</v>
       </c>
@@ -46370,7 +46364,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="140" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>2081</v>
       </c>
@@ -46642,7 +46636,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="141" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2085</v>
       </c>
@@ -46914,7 +46908,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="142" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2089</v>
       </c>
@@ -47186,7 +47180,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="143" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>2093</v>
       </c>
@@ -47458,7 +47452,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="144" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>2096</v>
       </c>
@@ -47730,7 +47724,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="145" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>2100</v>
       </c>
@@ -48005,7 +47999,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="146" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2104</v>
       </c>
@@ -48277,7 +48271,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="147" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>2108</v>
       </c>
@@ -48549,7 +48543,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="148" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>2112</v>
       </c>
@@ -48824,7 +48818,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="149" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>2116</v>
       </c>
@@ -49365,7 +49359,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="151" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>2124</v>
       </c>
@@ -49640,7 +49634,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="152" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>2128</v>
       </c>
@@ -49912,7 +49906,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="153" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>2132</v>
       </c>
@@ -50184,7 +50178,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="154" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>2136</v>
       </c>
@@ -50456,7 +50450,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="155" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>2140</v>
       </c>
@@ -50728,7 +50722,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="156" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>2143</v>
       </c>
@@ -51000,7 +50994,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="157" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>2147</v>
       </c>
@@ -51275,7 +51269,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="158" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>2151</v>
       </c>
@@ -51547,7 +51541,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="159" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>2155</v>
       </c>
@@ -51819,7 +51813,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="160" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>2159</v>
       </c>
@@ -52091,7 +52085,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="161" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>2163</v>
       </c>
@@ -52363,7 +52357,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="162" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>2166</v>
       </c>
@@ -52635,7 +52629,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="163" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>2170</v>
       </c>
@@ -52910,7 +52904,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="164" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>2174</v>
       </c>
@@ -53182,7 +53176,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="165" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>2178</v>
       </c>
@@ -53454,7 +53448,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="166" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>2182</v>
       </c>
@@ -53729,7 +53723,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="167" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>2186</v>
       </c>
@@ -54270,7 +54264,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="169" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>2194</v>
       </c>
@@ -54545,7 +54539,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="170" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>2198</v>
       </c>
@@ -54817,7 +54811,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="171" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>2202</v>
       </c>
@@ -55089,7 +55083,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="172" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>2206</v>
       </c>
@@ -55361,7 +55355,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="173" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>2210</v>
       </c>
@@ -55633,7 +55627,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="174" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>2213</v>
       </c>
@@ -55905,7 +55899,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="175" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>2217</v>
       </c>
@@ -56180,7 +56174,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="176" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>2221</v>
       </c>
@@ -56452,7 +56446,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="177" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>2225</v>
       </c>
@@ -56724,7 +56718,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="178" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>2229</v>
       </c>
@@ -56999,7 +56993,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="179" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>2233</v>
       </c>
@@ -57540,7 +57534,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="181" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>2241</v>
       </c>
@@ -57815,7 +57809,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="182" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>2245</v>
       </c>
@@ -58087,7 +58081,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="183" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>2249</v>
       </c>
@@ -58359,7 +58353,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="184" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>2253</v>
       </c>
@@ -58631,7 +58625,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="185" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>2257</v>
       </c>
@@ -58903,7 +58897,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="186" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>2260</v>
       </c>
@@ -59175,7 +59169,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="187" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>2264</v>
       </c>
@@ -59450,7 +59444,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="188" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>2268</v>
       </c>
@@ -59722,7 +59716,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="189" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>2272</v>
       </c>
@@ -59994,7 +59988,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="190" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>2276</v>
       </c>
@@ -60269,7 +60263,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="191" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>2280</v>
       </c>
@@ -60810,7 +60804,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="193" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>2288</v>
       </c>
@@ -61085,7 +61079,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="194" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>2292</v>
       </c>
@@ -61357,7 +61351,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="195" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>2296</v>
       </c>
@@ -61629,7 +61623,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="196" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>2300</v>
       </c>
@@ -61901,7 +61895,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="197" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>2304</v>
       </c>
@@ -62173,7 +62167,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="198" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>2307</v>
       </c>
@@ -62445,7 +62439,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="199" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>2311</v>
       </c>
@@ -62720,7 +62714,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="200" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>2315</v>
       </c>
@@ -62992,7 +62986,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="201" spans="1:91" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>2319</v>
       </c>
